--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/DELAWARE_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/DELAWARE_2015.xlsx
@@ -535,7 +535,7 @@
         <v>2</v>
       </c>
       <c r="D10">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="11">
@@ -553,7 +553,7 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="12">
@@ -625,7 +625,7 @@
         <v>2</v>
       </c>
       <c r="D15">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="16">
@@ -715,7 +715,7 @@
         <v>2</v>
       </c>
       <c r="D20">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="21">
@@ -787,7 +787,7 @@
         <v>2</v>
       </c>
       <c r="D24">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="25">
@@ -985,7 +985,7 @@
         <v>20</v>
       </c>
       <c r="D35">
-        <v>0.009237875288683603</v>
+        <v>0.009237875288683604</v>
       </c>
     </row>
     <row r="36">
@@ -1165,7 +1165,7 @@
         <v>2</v>
       </c>
       <c r="D45">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="46">
@@ -1183,7 +1183,7 @@
         <v>2</v>
       </c>
       <c r="D46">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="47">
@@ -1435,7 +1435,7 @@
         <v>2</v>
       </c>
       <c r="D60">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="61">
@@ -1453,7 +1453,7 @@
         <v>2</v>
       </c>
       <c r="D61">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="62">
@@ -1471,7 +1471,7 @@
         <v>2</v>
       </c>
       <c r="D62">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="63">
@@ -1507,7 +1507,7 @@
         <v>2</v>
       </c>
       <c r="D64">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="65">
@@ -1561,7 +1561,7 @@
         <v>2</v>
       </c>
       <c r="D67">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="68">
@@ -1579,7 +1579,7 @@
         <v>2</v>
       </c>
       <c r="D68">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="69">
@@ -1597,7 +1597,7 @@
         <v>2</v>
       </c>
       <c r="D69">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="70">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="D70">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="71">
@@ -1741,7 +1741,7 @@
         <v>2</v>
       </c>
       <c r="D77">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="78">
@@ -1777,7 +1777,7 @@
         <v>2</v>
       </c>
       <c r="D79">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="80">
@@ -1867,7 +1867,7 @@
         <v>2</v>
       </c>
       <c r="D84">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="85">
@@ -2047,7 +2047,7 @@
         <v>2</v>
       </c>
       <c r="D94">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="95">
@@ -2101,7 +2101,7 @@
         <v>2</v>
       </c>
       <c r="D97">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="98">
@@ -2227,7 +2227,7 @@
         <v>2</v>
       </c>
       <c r="D104">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="105">
@@ -2317,7 +2317,7 @@
         <v>2</v>
       </c>
       <c r="D109">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="110">
@@ -2515,7 +2515,7 @@
         <v>2</v>
       </c>
       <c r="D120">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="121">
@@ -2641,7 +2641,7 @@
         <v>2</v>
       </c>
       <c r="D127">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="128">
@@ -2713,7 +2713,7 @@
         <v>2</v>
       </c>
       <c r="D131">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="132">
@@ -2857,7 +2857,7 @@
         <v>2</v>
       </c>
       <c r="D139">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="140">
@@ -2911,7 +2911,7 @@
         <v>2</v>
       </c>
       <c r="D142">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="143">
@@ -3001,7 +3001,7 @@
         <v>2</v>
       </c>
       <c r="D147">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="148">
@@ -3127,7 +3127,7 @@
         <v>2</v>
       </c>
       <c r="D154">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="155">
@@ -3217,7 +3217,7 @@
         <v>2</v>
       </c>
       <c r="D159">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="160">
@@ -3487,7 +3487,7 @@
         <v>2</v>
       </c>
       <c r="D174">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="175">
@@ -3649,7 +3649,7 @@
         <v>2</v>
       </c>
       <c r="D183">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="184">
@@ -3685,7 +3685,7 @@
         <v>2</v>
       </c>
       <c r="D185">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="186">
@@ -3721,7 +3721,7 @@
         <v>2</v>
       </c>
       <c r="D187">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="188">
@@ -3775,7 +3775,7 @@
         <v>2</v>
       </c>
       <c r="D190">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="191">
@@ -3847,7 +3847,7 @@
         <v>2</v>
       </c>
       <c r="D194">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="195">
@@ -3901,7 +3901,7 @@
         <v>2</v>
       </c>
       <c r="D197">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="198">
@@ -3937,7 +3937,7 @@
         <v>2</v>
       </c>
       <c r="D199">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="200">
@@ -4045,7 +4045,7 @@
         <v>2</v>
       </c>
       <c r="D205">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="206">
@@ -4189,7 +4189,7 @@
         <v>2</v>
       </c>
       <c r="D213">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="214">
@@ -4297,7 +4297,7 @@
         <v>2</v>
       </c>
       <c r="D219">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="220">
@@ -4405,7 +4405,7 @@
         <v>2</v>
       </c>
       <c r="D225">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="226">
@@ -4423,7 +4423,7 @@
         <v>2</v>
       </c>
       <c r="D226">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="227">
@@ -4567,7 +4567,7 @@
         <v>2</v>
       </c>
       <c r="D234">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="235">
@@ -4657,7 +4657,7 @@
         <v>2</v>
       </c>
       <c r="D239">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="240">
@@ -4711,7 +4711,7 @@
         <v>2</v>
       </c>
       <c r="D242">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="243">
@@ -4729,7 +4729,7 @@
         <v>2</v>
       </c>
       <c r="D243">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="244">
@@ -4747,7 +4747,7 @@
         <v>2</v>
       </c>
       <c r="D244">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="245">
@@ -4891,7 +4891,7 @@
         <v>2</v>
       </c>
       <c r="D252">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="253">
@@ -4909,7 +4909,7 @@
         <v>2</v>
       </c>
       <c r="D253">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="254">
@@ -5035,7 +5035,7 @@
         <v>2</v>
       </c>
       <c r="D260">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="261">
@@ -5053,7 +5053,7 @@
         <v>2</v>
       </c>
       <c r="D261">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="262">
@@ -5125,7 +5125,7 @@
         <v>2</v>
       </c>
       <c r="D265">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="266">
@@ -5161,7 +5161,7 @@
         <v>20</v>
       </c>
       <c r="D267">
-        <v>0.009237875288683603</v>
+        <v>0.009237875288683604</v>
       </c>
     </row>
     <row r="268">
@@ -5269,7 +5269,7 @@
         <v>2</v>
       </c>
       <c r="D273">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="274">
@@ -5359,7 +5359,7 @@
         <v>2</v>
       </c>
       <c r="D278">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="279">
@@ -5431,7 +5431,7 @@
         <v>2</v>
       </c>
       <c r="D282">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="283">
@@ -5449,7 +5449,7 @@
         <v>2</v>
       </c>
       <c r="D283">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="284">
@@ -5521,7 +5521,7 @@
         <v>2</v>
       </c>
       <c r="D287">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="288">
@@ -5665,7 +5665,7 @@
         <v>2</v>
       </c>
       <c r="D295">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="296">
@@ -5719,7 +5719,7 @@
         <v>2</v>
       </c>
       <c r="D298">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="299">
@@ -5737,7 +5737,7 @@
         <v>2</v>
       </c>
       <c r="D299">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="300">
@@ -5809,7 +5809,7 @@
         <v>2</v>
       </c>
       <c r="D303">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="304">
@@ -5953,7 +5953,7 @@
         <v>2</v>
       </c>
       <c r="D311">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="312">
@@ -5971,7 +5971,7 @@
         <v>2</v>
       </c>
       <c r="D312">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="313">
@@ -6007,7 +6007,7 @@
         <v>2</v>
       </c>
       <c r="D314">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="315">
@@ -6025,7 +6025,7 @@
         <v>2</v>
       </c>
       <c r="D315">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="316">
@@ -6133,7 +6133,7 @@
         <v>2</v>
       </c>
       <c r="D321">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="322">
@@ -6169,7 +6169,7 @@
         <v>2</v>
       </c>
       <c r="D323">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="324">
@@ -6187,7 +6187,7 @@
         <v>2</v>
       </c>
       <c r="D324">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="325">
@@ -6259,7 +6259,7 @@
         <v>2</v>
       </c>
       <c r="D328">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="329">
@@ -6493,7 +6493,7 @@
         <v>2</v>
       </c>
       <c r="D341">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="342">
@@ -6601,7 +6601,7 @@
         <v>2</v>
       </c>
       <c r="D347">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="348">
@@ -6691,7 +6691,7 @@
         <v>2</v>
       </c>
       <c r="D352">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="353">
@@ -6727,7 +6727,7 @@
         <v>2</v>
       </c>
       <c r="D354">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="355">
@@ -6781,7 +6781,7 @@
         <v>2</v>
       </c>
       <c r="D357">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="358">
@@ -7033,7 +7033,7 @@
         <v>2</v>
       </c>
       <c r="D371">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="372">
@@ -7051,7 +7051,7 @@
         <v>2</v>
       </c>
       <c r="D372">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="373">
@@ -7231,7 +7231,7 @@
         <v>2</v>
       </c>
       <c r="D382">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="383">
@@ -7285,7 +7285,7 @@
         <v>2</v>
       </c>
       <c r="D385">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="386">
@@ -7357,7 +7357,7 @@
         <v>2</v>
       </c>
       <c r="D389">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="390">
@@ -7375,7 +7375,7 @@
         <v>2</v>
       </c>
       <c r="D390">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="391">
@@ -7429,7 +7429,7 @@
         <v>2</v>
       </c>
       <c r="D393">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="394">
@@ -7771,7 +7771,7 @@
         <v>2</v>
       </c>
       <c r="D412">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="413">
@@ -7933,7 +7933,7 @@
         <v>2</v>
       </c>
       <c r="D421">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="422">
@@ -8149,7 +8149,7 @@
         <v>2</v>
       </c>
       <c r="D433">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="434">
@@ -8203,7 +8203,7 @@
         <v>2</v>
       </c>
       <c r="D436">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="437">
@@ -8347,7 +8347,7 @@
         <v>2</v>
       </c>
       <c r="D444">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="445">
@@ -8419,7 +8419,7 @@
         <v>2</v>
       </c>
       <c r="D448">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="449">
@@ -8599,7 +8599,7 @@
         <v>2</v>
       </c>
       <c r="D458">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="459">
@@ -8635,7 +8635,7 @@
         <v>2</v>
       </c>
       <c r="D460">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="461">
@@ -8707,7 +8707,7 @@
         <v>2</v>
       </c>
       <c r="D464">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="465">
@@ -8743,7 +8743,7 @@
         <v>2</v>
       </c>
       <c r="D466">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="467">
@@ -8797,7 +8797,7 @@
         <v>2</v>
       </c>
       <c r="D469">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="470">
@@ -8905,7 +8905,7 @@
         <v>2</v>
       </c>
       <c r="D475">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="476">
@@ -9049,7 +9049,7 @@
         <v>2</v>
       </c>
       <c r="D483">
-        <v>0.0009237875288683603</v>
+        <v>0.0009237875288683604</v>
       </c>
     </row>
     <row r="484">
